--- a/Jide Jegede advanced_sales_dataset.xlsx
+++ b/Jide Jegede advanced_sales_dataset.xlsx
@@ -9,26 +9,27 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7310" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7310"/>
   </bookViews>
   <sheets>
-    <sheet name="Advanced Sales Data" sheetId="1" r:id="rId1"/>
-    <sheet name="PIVOT TABLE" sheetId="8" r:id="rId2"/>
-    <sheet name="DASHBOARD" sheetId="9" r:id="rId3"/>
+    <sheet name="Raw Data" sheetId="10" r:id="rId1"/>
+    <sheet name="Advanced Sales Data" sheetId="1" r:id="rId2"/>
+    <sheet name="PIVOT TABLE" sheetId="8" r:id="rId3"/>
+    <sheet name="DASHBOARD" sheetId="9" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="Slicer_Category">#N/A</definedName>
     <definedName name="Slicer_Customer_Name">#N/A</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual"/>
+  <calcPr calcId="152511"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId4"/>
+    <pivotCache cacheId="0" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
       <x14:slicerCaches>
-        <x14:slicerCache r:id="rId5"/>
         <x14:slicerCache r:id="rId6"/>
+        <x14:slicerCache r:id="rId7"/>
       </x14:slicerCaches>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="886" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1859" uniqueCount="137">
   <si>
     <t>Date</t>
   </si>
@@ -151,6 +152,306 @@
   <si>
     <t>DATA VISUALIZATION</t>
   </si>
+  <si>
+    <t>2025-01-06</t>
+  </si>
+  <si>
+    <t>2025-01-07</t>
+  </si>
+  <si>
+    <t>ABUJA</t>
+  </si>
+  <si>
+    <t>2025-01-08</t>
+  </si>
+  <si>
+    <t>2025-01-10</t>
+  </si>
+  <si>
+    <t>lagos</t>
+  </si>
+  <si>
+    <t>2025-01-11</t>
+  </si>
+  <si>
+    <t>2025-01-12</t>
+  </si>
+  <si>
+    <t>2025-01-15</t>
+  </si>
+  <si>
+    <t>2025-01-16</t>
+  </si>
+  <si>
+    <t>2025-01-18</t>
+  </si>
+  <si>
+    <t>2025-01-19</t>
+  </si>
+  <si>
+    <t>2025-01-23</t>
+  </si>
+  <si>
+    <t>2025-01-24</t>
+  </si>
+  <si>
+    <t>2025-01-25</t>
+  </si>
+  <si>
+    <t>2025-01-28</t>
+  </si>
+  <si>
+    <t>2025-01-30</t>
+  </si>
+  <si>
+    <t>2025-01-31</t>
+  </si>
+  <si>
+    <t>2025-02-01</t>
+  </si>
+  <si>
+    <t>2025-02-02</t>
+  </si>
+  <si>
+    <t>2025-02-03</t>
+  </si>
+  <si>
+    <t>2025-02-04</t>
+  </si>
+  <si>
+    <t>2025-02-07</t>
+  </si>
+  <si>
+    <t>2025-02-09</t>
+  </si>
+  <si>
+    <t>2025-02-10</t>
+  </si>
+  <si>
+    <t>2025-02-11</t>
+  </si>
+  <si>
+    <t>2025-02-13</t>
+  </si>
+  <si>
+    <t>2025-02-15</t>
+  </si>
+  <si>
+    <t>2025-02-16</t>
+  </si>
+  <si>
+    <t>2025-02-18</t>
+  </si>
+  <si>
+    <t>2025-02-20</t>
+  </si>
+  <si>
+    <t>2025-02-22</t>
+  </si>
+  <si>
+    <t>2025-02-23</t>
+  </si>
+  <si>
+    <t>2025-02-24</t>
+  </si>
+  <si>
+    <t>2025-02-25</t>
+  </si>
+  <si>
+    <t>2025-02-26</t>
+  </si>
+  <si>
+    <t>2025-02-27</t>
+  </si>
+  <si>
+    <t>2025-02-28</t>
+  </si>
+  <si>
+    <t>2025-03-01</t>
+  </si>
+  <si>
+    <t>2025-03-03</t>
+  </si>
+  <si>
+    <t>2025-03-04</t>
+  </si>
+  <si>
+    <t>2025-03-05</t>
+  </si>
+  <si>
+    <t>2025-03-08</t>
+  </si>
+  <si>
+    <t>2025-03-09</t>
+  </si>
+  <si>
+    <t>2025-03-11</t>
+  </si>
+  <si>
+    <t>2025-03-12</t>
+  </si>
+  <si>
+    <t>2025-03-13</t>
+  </si>
+  <si>
+    <t>2025-03-14</t>
+  </si>
+  <si>
+    <t>2025-03-15</t>
+  </si>
+  <si>
+    <t>2025-03-16</t>
+  </si>
+  <si>
+    <t>2025-03-18</t>
+  </si>
+  <si>
+    <t>2025-03-20</t>
+  </si>
+  <si>
+    <t>2025-03-23</t>
+  </si>
+  <si>
+    <t>2025-03-24</t>
+  </si>
+  <si>
+    <t>2025-03-25</t>
+  </si>
+  <si>
+    <t>2025-03-27</t>
+  </si>
+  <si>
+    <t>2025-03-29</t>
+  </si>
+  <si>
+    <t>2025-03-30</t>
+  </si>
+  <si>
+    <t>2025-04-01</t>
+  </si>
+  <si>
+    <t>2025-04-03</t>
+  </si>
+  <si>
+    <t>2025-04-04</t>
+  </si>
+  <si>
+    <t>2025-04-06</t>
+  </si>
+  <si>
+    <t>2025-04-07</t>
+  </si>
+  <si>
+    <t>2025-04-09</t>
+  </si>
+  <si>
+    <t>2025-04-10</t>
+  </si>
+  <si>
+    <t>2025-04-11</t>
+  </si>
+  <si>
+    <t>2025-04-12</t>
+  </si>
+  <si>
+    <t>2025-04-14</t>
+  </si>
+  <si>
+    <t>2025-04-15</t>
+  </si>
+  <si>
+    <t>2025-04-16</t>
+  </si>
+  <si>
+    <t>2025-04-17</t>
+  </si>
+  <si>
+    <t>2025-04-18</t>
+  </si>
+  <si>
+    <t>2025-04-21</t>
+  </si>
+  <si>
+    <t>2025-04-22</t>
+  </si>
+  <si>
+    <t>2025-04-23</t>
+  </si>
+  <si>
+    <t>2025-04-24</t>
+  </si>
+  <si>
+    <t>2025-04-25</t>
+  </si>
+  <si>
+    <t>2025-04-26</t>
+  </si>
+  <si>
+    <t>2025-04-27</t>
+  </si>
+  <si>
+    <t>2025-04-28</t>
+  </si>
+  <si>
+    <t>2025-04-29</t>
+  </si>
+  <si>
+    <t>2025-05-01</t>
+  </si>
+  <si>
+    <t>2025-05-03</t>
+  </si>
+  <si>
+    <t>2025-05-04</t>
+  </si>
+  <si>
+    <t>2025-05-06</t>
+  </si>
+  <si>
+    <t>2025-05-07</t>
+  </si>
+  <si>
+    <t>2025-05-08</t>
+  </si>
+  <si>
+    <t>2025-05-09</t>
+  </si>
+  <si>
+    <t>2025-05-10</t>
+  </si>
+  <si>
+    <t>2025-05-11</t>
+  </si>
+  <si>
+    <t>2025-05-12</t>
+  </si>
+  <si>
+    <t>2025-05-16</t>
+  </si>
+  <si>
+    <t>2025-05-17</t>
+  </si>
+  <si>
+    <t>2025-05-18</t>
+  </si>
+  <si>
+    <t>2025-05-19</t>
+  </si>
+  <si>
+    <t>2025-05-24</t>
+  </si>
+  <si>
+    <t>2025-05-25</t>
+  </si>
+  <si>
+    <t>2025-05-28</t>
+  </si>
+  <si>
+    <t>2025-05-29</t>
+  </si>
+  <si>
+    <t>2025-05-30</t>
+  </si>
 </sst>
 </file>
 
@@ -162,7 +463,7 @@
     <numFmt numFmtId="166" formatCode="[$₦-466]\ #,##0.00"/>
     <numFmt numFmtId="167" formatCode="&quot;₦&quot;#,##0.00,,&quot;M&quot;"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -200,6 +501,17 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptow"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptow"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -233,7 +545,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -266,161 +578,16 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="66">
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;₦&quot;#,##0.00,,&quot;M&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;₦&quot;#,##0.00,,&quot;M&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="[$₦-46A]#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="[$₦-466]\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;₦&quot;#,##0.00,,&quot;M&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;₦&quot;#,##0.00,,&quot;M&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;₦&quot;#,##0.00,,&quot;M&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;₦&quot;#,##0.00,,&quot;M&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="[$₦-46A]#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="[$₦-466]\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;₦&quot;#,##0.00,,&quot;M&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;₦&quot;#,##0.00,,&quot;M&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="[$₦-46A]#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="[$₦-466]\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;₦&quot;#,##0.00,,&quot;M&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;₦&quot;#,##0.00,,&quot;M&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;₦&quot;#,##0.00,,&quot;M&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;₦&quot;#,##0.00,,&quot;M&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="[$₦-46A]#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="[$₦-466]\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;₦&quot;#,##0.00,,&quot;M&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;₦&quot;#,##0.00,,&quot;M&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="[$₦-46A]#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="[$₦-466]\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;₦&quot;#,##0.00,,&quot;M&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;₦&quot;#,##0.00,,&quot;M&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;₦&quot;#,##0.00,,&quot;M&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;₦&quot;#,##0.00,,&quot;M&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="[$₦-46A]#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="[$₦-466]\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;₦&quot;#,##0.00,,&quot;M&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;₦&quot;#,##0.00,,&quot;M&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="[$₦-46A]#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="[$₦-466]\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;₦&quot;#,##0.00,,&quot;M&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;₦&quot;#,##0.00,,&quot;M&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;₦&quot;#,##0.00,,&quot;M&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;₦&quot;#,##0.00,,&quot;M&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="[$₦-46A]#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="[$₦-466]\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;₦&quot;#,##0.00,,&quot;M&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;₦&quot;#,##0.00,,&quot;M&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="[$₦-46A]#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="[$₦-466]\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;₦&quot;#,##0.00,,&quot;M&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;₦&quot;#,##0.00,,&quot;M&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;₦&quot;#,##0.00,,&quot;M&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;₦&quot;#,##0.00,,&quot;M&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="[$₦-46A]#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="[$₦-466]\ #,##0.00"/>
-    </dxf>
+  <dxfs count="16">
     <dxf>
       <numFmt numFmtId="167" formatCode="&quot;₦&quot;#,##0.00,,&quot;M&quot;"/>
     </dxf>
@@ -502,10 +669,10 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Slicer Style 1" pivot="0" table="0" count="4">
-      <tableStyleElement type="wholeTable" dxfId="65"/>
+      <tableStyleElement type="wholeTable" dxfId="15"/>
     </tableStyle>
     <tableStyle name="Slicer Style 2" pivot="0" table="0" count="4">
-      <tableStyleElement type="wholeTable" dxfId="64"/>
+      <tableStyleElement type="wholeTable" dxfId="14"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -994,11 +1161,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="182"/>
-        <c:axId val="365134584"/>
-        <c:axId val="365133800"/>
+        <c:axId val="364228224"/>
+        <c:axId val="364229792"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="365134584"/>
+        <c:axId val="364228224"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1040,7 +1207,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="365133800"/>
+        <c:crossAx val="364229792"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1048,7 +1215,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="365133800"/>
+        <c:axId val="364229792"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1058,7 +1225,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="365134584"/>
+        <c:crossAx val="364228224"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1412,11 +1579,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="219"/>
-        <c:axId val="365137328"/>
-        <c:axId val="365135368"/>
+        <c:axId val="393735056"/>
+        <c:axId val="393734272"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="365137328"/>
+        <c:axId val="393735056"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1458,7 +1625,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="365135368"/>
+        <c:crossAx val="393734272"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1466,7 +1633,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="365135368"/>
+        <c:axId val="393734272"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1490,7 +1657,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="365137328"/>
+        <c:crossAx val="393735056"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5535,10 +5702,10 @@
     <dataField name="Sum of Total Sales" fld="6" baseField="0" baseItem="0" numFmtId="167"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="51">
+    <format dxfId="1">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="50">
+    <format dxfId="0">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -5640,10 +5807,10 @@
     <dataField name="Sum of Total Sales" fld="6" baseField="0" baseItem="0" numFmtId="166"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="53">
+    <format dxfId="3">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="52">
+    <format dxfId="2">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -5710,10 +5877,10 @@
     <dataField name="Sum of Total Sales" fld="6" baseField="0" baseItem="0" numFmtId="167"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="55">
+    <format dxfId="5">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="54">
+    <format dxfId="4">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -5769,10 +5936,10 @@
     <dataField name="Sum of Total Sales" fld="6" baseField="0" baseItem="0" numFmtId="166"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="57">
+    <format dxfId="7">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="56">
+    <format dxfId="6">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -5858,10 +6025,10 @@
     <dataField name="Sum of Total Sales" fld="6" baseField="0" baseItem="0" numFmtId="167"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="59">
+    <format dxfId="9">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="58">
+    <format dxfId="8">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -5981,7 +6148,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:I200" totalsRowShown="0" headerRowDxfId="63">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:I200" totalsRowShown="0" headerRowDxfId="13">
   <autoFilter ref="A1:I200"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Date"/>
@@ -5989,12 +6156,12 @@
     <tableColumn id="3" name="Product"/>
     <tableColumn id="4" name="Category"/>
     <tableColumn id="5" name="Quantity"/>
-    <tableColumn id="6" name="Unit Price" dataDxfId="62"/>
-    <tableColumn id="7" name="Total Sales" dataDxfId="61">
+    <tableColumn id="6" name="Unit Price" dataDxfId="12"/>
+    <tableColumn id="7" name="Total Sales" dataDxfId="11">
       <calculatedColumnFormula>E2*F2</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="8" name="Region"/>
-    <tableColumn id="11" name="Discount" dataDxfId="60">
+    <tableColumn id="11" name="Discount" dataDxfId="10">
       <calculatedColumnFormula>IF(G2&gt;=100000,G2*VLOOKUP(H2,$L$1:$M$7,2,FALSE),"No Discount")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6287,8 +6454,4487 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G201"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.6328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="18" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="19">
+        <v>5</v>
+      </c>
+      <c r="F2" s="19">
+        <v>204140.09</v>
+      </c>
+      <c r="G2" s="19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="19">
+        <v>5</v>
+      </c>
+      <c r="F3" s="19">
+        <v>8159.96</v>
+      </c>
+      <c r="G3" s="19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="19">
+        <v>3</v>
+      </c>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="19">
+        <v>0</v>
+      </c>
+      <c r="F5" s="19">
+        <v>7020</v>
+      </c>
+      <c r="G5" s="19" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="19">
+        <v>10</v>
+      </c>
+      <c r="F6" s="19">
+        <v>13927.77</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="19">
+        <v>5</v>
+      </c>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="19">
+        <v>10</v>
+      </c>
+      <c r="F8" s="19">
+        <v>13767.94</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="19">
+        <v>1</v>
+      </c>
+      <c r="F9" s="19">
+        <v>12658.08</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="19">
+        <v>5</v>
+      </c>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="19">
+        <v>2</v>
+      </c>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="20">
+        <v>45670</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="19">
+        <v>5</v>
+      </c>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" s="19">
+        <v>1</v>
+      </c>
+      <c r="F13" s="19">
+        <v>91767.26</v>
+      </c>
+      <c r="G13" s="19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="19">
+        <v>-1</v>
+      </c>
+      <c r="F14" s="19">
+        <v>195995.82</v>
+      </c>
+      <c r="G14" s="19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="19">
+        <v>7</v>
+      </c>
+      <c r="F15" s="19">
+        <v>13189.05</v>
+      </c>
+      <c r="G15" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16" s="19">
+        <v>2</v>
+      </c>
+      <c r="F16" s="19">
+        <v>44765.47</v>
+      </c>
+      <c r="G16" s="19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" s="19">
+        <v>4</v>
+      </c>
+      <c r="F17" s="19">
+        <v>90133.86</v>
+      </c>
+      <c r="G17" s="19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" s="19">
+        <v>5</v>
+      </c>
+      <c r="F18" s="19">
+        <v>16952.41</v>
+      </c>
+      <c r="G18" s="19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" s="19">
+        <v>10</v>
+      </c>
+      <c r="F19" s="19">
+        <v>193020.41</v>
+      </c>
+      <c r="G19" s="19" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" s="19">
+        <v>0</v>
+      </c>
+      <c r="F20" s="19">
+        <v>314132.18</v>
+      </c>
+      <c r="G20" s="19" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="19">
+        <v>7</v>
+      </c>
+      <c r="F21" s="19">
+        <v>87243.92</v>
+      </c>
+      <c r="G21" s="19"/>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E22" s="19">
+        <v>1</v>
+      </c>
+      <c r="F22" s="19"/>
+      <c r="G22" s="19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E23" s="19">
+        <v>5</v>
+      </c>
+      <c r="F23" s="19">
+        <v>79645.63</v>
+      </c>
+      <c r="G23" s="19" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D24" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E24" s="19">
+        <v>3</v>
+      </c>
+      <c r="F24" s="19">
+        <v>39663.14</v>
+      </c>
+      <c r="G24" s="19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D25" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25" s="19">
+        <v>8</v>
+      </c>
+      <c r="F25" s="19">
+        <v>76173.37</v>
+      </c>
+      <c r="G25" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C26" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D26" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" s="19">
+        <v>9</v>
+      </c>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D27" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" s="19">
+        <v>5</v>
+      </c>
+      <c r="F27" s="19">
+        <v>388950.08</v>
+      </c>
+      <c r="G27" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D28" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" s="19">
+        <v>5</v>
+      </c>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="B29" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C29" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="D29" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" s="19">
+        <v>7</v>
+      </c>
+      <c r="F29" s="19">
+        <v>179016.2</v>
+      </c>
+      <c r="G29" s="19"/>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="B30" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C30" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D30" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" s="19">
+        <v>5</v>
+      </c>
+      <c r="F30" s="19">
+        <v>383639.73</v>
+      </c>
+      <c r="G30" s="19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="B31" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D31" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E31" s="19">
+        <v>10</v>
+      </c>
+      <c r="F31" s="19">
+        <v>11105.06</v>
+      </c>
+      <c r="G31" s="19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="B32" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="C32" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E32" s="19">
+        <v>7</v>
+      </c>
+      <c r="F32" s="19">
+        <v>8009.15</v>
+      </c>
+      <c r="G32" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="B33" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D33" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" s="19">
+        <v>3</v>
+      </c>
+      <c r="F33" s="19">
+        <v>321202.15999999997</v>
+      </c>
+      <c r="G33" s="19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="B34" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C34" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D34" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E34" s="19">
+        <v>2</v>
+      </c>
+      <c r="F34" s="19">
+        <v>12963.47</v>
+      </c>
+      <c r="G34" s="19" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="B35" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C35" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D35" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E35" s="19">
+        <v>10</v>
+      </c>
+      <c r="F35" s="19">
+        <v>15291.86</v>
+      </c>
+      <c r="G35" s="19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="B36" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="D36" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E36" s="19">
+        <v>3</v>
+      </c>
+      <c r="F36" s="19"/>
+      <c r="G36" s="19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="B37" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D37" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E37" s="19">
+        <v>3</v>
+      </c>
+      <c r="F37" s="19">
+        <v>12524.88</v>
+      </c>
+      <c r="G37" s="19" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="B38" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="C38" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D38" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E38" s="19">
+        <v>5</v>
+      </c>
+      <c r="F38" s="19">
+        <v>85057.33</v>
+      </c>
+      <c r="G38" s="19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="B39" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="D39" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E39" s="19">
+        <v>5</v>
+      </c>
+      <c r="F39" s="19">
+        <v>73299.990000000005</v>
+      </c>
+      <c r="G39" s="19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="B40" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C40" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E40" s="19">
+        <v>9</v>
+      </c>
+      <c r="F40" s="19">
+        <v>7040.92</v>
+      </c>
+      <c r="G40" s="19" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="B41" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C41" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D41" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E41" s="19">
+        <v>6</v>
+      </c>
+      <c r="F41" s="19">
+        <v>13062.14</v>
+      </c>
+      <c r="G41" s="19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="B42" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C42" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D42" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E42" s="19">
+        <v>2</v>
+      </c>
+      <c r="F42" s="19">
+        <v>76356.73</v>
+      </c>
+      <c r="G42" s="19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="B43" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="C43" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D43" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E43" s="19">
+        <v>1</v>
+      </c>
+      <c r="F43" s="19">
+        <v>13482.82</v>
+      </c>
+      <c r="G43" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="B44" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C44" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D44" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E44" s="19">
+        <v>8</v>
+      </c>
+      <c r="F44" s="19">
+        <v>105878.62</v>
+      </c>
+      <c r="G44" s="19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="B45" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D45" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E45" s="19">
+        <v>8</v>
+      </c>
+      <c r="F45" s="19">
+        <v>11955.67</v>
+      </c>
+      <c r="G45" s="19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="B46" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C46" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="D46" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E46" s="19">
+        <v>7</v>
+      </c>
+      <c r="F46" s="19"/>
+      <c r="G46" s="19" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="B47" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C47" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D47" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E47" s="19">
+        <v>4</v>
+      </c>
+      <c r="F47" s="19">
+        <v>11190.13</v>
+      </c>
+      <c r="G47" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="B48" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="C48" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D48" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E48" s="19">
+        <v>4</v>
+      </c>
+      <c r="F48" s="19">
+        <v>49789.24</v>
+      </c>
+      <c r="G48" s="19"/>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="B49" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C49" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E49" s="19">
+        <v>10</v>
+      </c>
+      <c r="F49" s="19">
+        <v>7286.17</v>
+      </c>
+      <c r="G49" s="19"/>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="B50" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C50" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D50" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E50" s="19">
+        <v>5</v>
+      </c>
+      <c r="F50" s="19">
+        <v>316216.90999999997</v>
+      </c>
+      <c r="G50" s="19" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="B51" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C51" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D51" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E51" s="19">
+        <v>6</v>
+      </c>
+      <c r="F51" s="19"/>
+      <c r="G51" s="19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="B52" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C52" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="D52" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E52" s="19">
+        <v>9</v>
+      </c>
+      <c r="F52" s="19"/>
+      <c r="G52" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="B53" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C53" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D53" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E53" s="19">
+        <v>10</v>
+      </c>
+      <c r="F53" s="19"/>
+      <c r="G53" s="19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="B54" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C54" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D54" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E54" s="19">
+        <v>7</v>
+      </c>
+      <c r="F54" s="19">
+        <v>13515.87</v>
+      </c>
+      <c r="G54" s="19"/>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="B55" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C55" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D55" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E55" s="19">
+        <v>4</v>
+      </c>
+      <c r="F55" s="19">
+        <v>13057.78</v>
+      </c>
+      <c r="G55" s="19" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="B56" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="C56" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D56" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E56" s="19">
+        <v>10</v>
+      </c>
+      <c r="F56" s="19">
+        <v>15980.14</v>
+      </c>
+      <c r="G56" s="19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="B57" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C57" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D57" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E57" s="19">
+        <v>7</v>
+      </c>
+      <c r="F57" s="19">
+        <v>16026.02</v>
+      </c>
+      <c r="G57" s="19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="B58" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C58" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D58" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E58" s="19">
+        <v>7</v>
+      </c>
+      <c r="F58" s="19">
+        <v>80872.61</v>
+      </c>
+      <c r="G58" s="19"/>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="B59" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C59" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D59" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E59" s="19">
+        <v>2</v>
+      </c>
+      <c r="F59" s="19">
+        <v>106607.48</v>
+      </c>
+      <c r="G59" s="19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="B60" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C60" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D60" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E60" s="19">
+        <v>1</v>
+      </c>
+      <c r="F60" s="19">
+        <v>15976.72</v>
+      </c>
+      <c r="G60" s="19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="B61" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C61" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D61" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E61" s="19">
+        <v>6</v>
+      </c>
+      <c r="F61" s="19"/>
+      <c r="G61" s="19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="B62" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C62" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D62" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E62" s="19">
+        <v>4</v>
+      </c>
+      <c r="F62" s="19">
+        <v>11884.61</v>
+      </c>
+      <c r="G62" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="B63" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C63" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D63" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E63" s="19">
+        <v>2</v>
+      </c>
+      <c r="F63" s="19">
+        <v>14934.23</v>
+      </c>
+      <c r="G63" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="B64" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C64" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D64" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E64" s="19">
+        <v>3</v>
+      </c>
+      <c r="F64" s="19">
+        <v>15792.03</v>
+      </c>
+      <c r="G64" s="19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="B65" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C65" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D65" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E65" s="19">
+        <v>0</v>
+      </c>
+      <c r="F65" s="19">
+        <v>383679.59</v>
+      </c>
+      <c r="G65" s="19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
+      <c r="A66" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="B66" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D66" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E66" s="19">
+        <v>6</v>
+      </c>
+      <c r="F66" s="19">
+        <v>339552.57</v>
+      </c>
+      <c r="G66" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
+      <c r="A67" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="B67" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="C67" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D67" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E67" s="19">
+        <v>1</v>
+      </c>
+      <c r="F67" s="19">
+        <v>15886.27</v>
+      </c>
+      <c r="G67" s="19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
+      <c r="A68" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="B68" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C68" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="D68" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E68" s="19">
+        <v>8</v>
+      </c>
+      <c r="F68" s="19"/>
+      <c r="G68" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
+      <c r="A69" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="B69" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C69" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D69" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E69" s="19">
+        <v>10</v>
+      </c>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
+      <c r="A70" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="B70" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D70" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E70" s="19">
+        <v>7</v>
+      </c>
+      <c r="F70" s="19">
+        <v>17221.41</v>
+      </c>
+      <c r="G70" s="19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7">
+      <c r="A71" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="B71" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C71" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D71" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E71" s="19">
+        <v>7</v>
+      </c>
+      <c r="F71" s="19">
+        <v>335230.39</v>
+      </c>
+      <c r="G71" s="19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
+      <c r="A72" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="B72" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="C72" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D72" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E72" s="19">
+        <v>9</v>
+      </c>
+      <c r="F72" s="19"/>
+      <c r="G72" s="19"/>
+    </row>
+    <row r="73" spans="1:7">
+      <c r="A73" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="B73" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C73" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D73" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E73" s="19">
+        <v>5</v>
+      </c>
+      <c r="F73" s="19">
+        <v>374619.09</v>
+      </c>
+      <c r="G73" s="19"/>
+    </row>
+    <row r="74" spans="1:7">
+      <c r="A74" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="B74" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C74" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D74" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E74" s="19">
+        <v>1</v>
+      </c>
+      <c r="F74" s="19">
+        <v>322447.65000000002</v>
+      </c>
+      <c r="G74" s="19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
+      <c r="A75" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="B75" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="C75" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D75" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E75" s="19">
+        <v>6</v>
+      </c>
+      <c r="F75" s="19">
+        <v>9199.8700000000008</v>
+      </c>
+      <c r="G75" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7">
+      <c r="A76" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="B76" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="C76" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D76" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E76" s="19">
+        <v>5</v>
+      </c>
+      <c r="F76" s="19"/>
+      <c r="G76" s="19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7">
+      <c r="A77" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="B77" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C77" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D77" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E77" s="19">
+        <v>9</v>
+      </c>
+      <c r="F77" s="19">
+        <v>303650.28999999998</v>
+      </c>
+      <c r="G77" s="19" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7">
+      <c r="A78" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="B78" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="C78" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D78" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E78" s="19">
+        <v>3</v>
+      </c>
+      <c r="F78" s="19">
+        <v>15469.86</v>
+      </c>
+      <c r="G78" s="19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7">
+      <c r="A79" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="B79" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C79" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D79" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E79" s="19">
+        <v>8</v>
+      </c>
+      <c r="F79" s="19"/>
+      <c r="G79" s="19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7">
+      <c r="A80" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="B80" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C80" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D80" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E80" s="19">
+        <v>6</v>
+      </c>
+      <c r="F80" s="19">
+        <v>8809.18</v>
+      </c>
+      <c r="G80" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7">
+      <c r="A81" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="B81" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C81" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D81" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E81" s="19">
+        <v>7</v>
+      </c>
+      <c r="F81" s="19">
+        <v>14907.33</v>
+      </c>
+      <c r="G81" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7">
+      <c r="A82" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="B82" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C82" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D82" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E82" s="19">
+        <v>4</v>
+      </c>
+      <c r="F82" s="19">
+        <v>49113.74</v>
+      </c>
+      <c r="G82" s="19"/>
+    </row>
+    <row r="83" spans="1:7">
+      <c r="A83" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="B83" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C83" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D83" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E83" s="19">
+        <v>10</v>
+      </c>
+      <c r="F83" s="19">
+        <v>85269.65</v>
+      </c>
+      <c r="G83" s="19" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7">
+      <c r="A84" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="B84" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C84" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D84" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E84" s="19">
+        <v>6</v>
+      </c>
+      <c r="F84" s="19">
+        <v>320845.82</v>
+      </c>
+      <c r="G84" s="19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7">
+      <c r="A85" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="B85" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C85" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="D85" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E85" s="19">
+        <v>5</v>
+      </c>
+      <c r="F85" s="19"/>
+      <c r="G85" s="19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7">
+      <c r="A86" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="B86" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="C86" s="19"/>
+      <c r="D86" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E86" s="19">
+        <v>6</v>
+      </c>
+      <c r="F86" s="19">
+        <v>42407.83</v>
+      </c>
+      <c r="G86" s="19"/>
+    </row>
+    <row r="87" spans="1:7">
+      <c r="A87" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="B87" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C87" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="D87" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E87" s="19">
+        <v>1</v>
+      </c>
+      <c r="F87" s="19"/>
+      <c r="G87" s="19" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7">
+      <c r="A88" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="B88" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C88" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D88" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E88" s="19">
+        <v>1</v>
+      </c>
+      <c r="F88" s="19">
+        <v>9102.31</v>
+      </c>
+      <c r="G88" s="19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7">
+      <c r="A89" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="B89" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C89" s="19"/>
+      <c r="D89" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E89" s="19">
+        <v>3</v>
+      </c>
+      <c r="F89" s="19"/>
+      <c r="G89" s="19"/>
+    </row>
+    <row r="90" spans="1:7">
+      <c r="A90" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="B90" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C90" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D90" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E90" s="19">
+        <v>4</v>
+      </c>
+      <c r="F90" s="19">
+        <v>11086.19</v>
+      </c>
+      <c r="G90" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7">
+      <c r="A91" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="B91" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C91" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D91" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E91" s="19">
+        <v>3</v>
+      </c>
+      <c r="F91" s="19">
+        <v>343709.26</v>
+      </c>
+      <c r="G91" s="19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7">
+      <c r="A92" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="B92" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="C92" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D92" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E92" s="19">
+        <v>4</v>
+      </c>
+      <c r="F92" s="19">
+        <v>49205.08</v>
+      </c>
+      <c r="G92" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7">
+      <c r="A93" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="B93" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="C93" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D93" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E93" s="19">
+        <v>4</v>
+      </c>
+      <c r="F93" s="19">
+        <v>102358.45</v>
+      </c>
+      <c r="G93" s="19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7">
+      <c r="A94" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="B94" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C94" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D94" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E94" s="19">
+        <v>3</v>
+      </c>
+      <c r="F94" s="19">
+        <v>89308.63</v>
+      </c>
+      <c r="G94" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7">
+      <c r="A95" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="B95" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C95" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D95" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E95" s="19">
+        <v>5</v>
+      </c>
+      <c r="F95" s="19">
+        <v>77011.75</v>
+      </c>
+      <c r="G95" s="19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7">
+      <c r="A96" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="B96" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C96" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D96" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E96" s="19">
+        <v>3</v>
+      </c>
+      <c r="F96" s="19">
+        <v>14627.54</v>
+      </c>
+      <c r="G96" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7">
+      <c r="A97" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="B97" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C97" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D97" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E97" s="19">
+        <v>9</v>
+      </c>
+      <c r="F97" s="19">
+        <v>81867.19</v>
+      </c>
+      <c r="G97" s="19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7">
+      <c r="A98" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="B98" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C98" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D98" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E98" s="19">
+        <v>-1</v>
+      </c>
+      <c r="F98" s="19">
+        <v>15069.49</v>
+      </c>
+      <c r="G98" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7">
+      <c r="A99" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="B99" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C99" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D99" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E99" s="19">
+        <v>7</v>
+      </c>
+      <c r="F99" s="19">
+        <v>11015.52</v>
+      </c>
+      <c r="G99" s="19" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7">
+      <c r="A100" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="B100" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C100" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D100" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E100" s="19">
+        <v>3</v>
+      </c>
+      <c r="F100" s="19">
+        <v>88708.41</v>
+      </c>
+      <c r="G100" s="19" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7">
+      <c r="A101" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="B101" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C101" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D101" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E101" s="19">
+        <v>10</v>
+      </c>
+      <c r="F101" s="19">
+        <v>105158.68</v>
+      </c>
+      <c r="G101" s="19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7">
+      <c r="A102" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="B102" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C102" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D102" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E102" s="19">
+        <v>6</v>
+      </c>
+      <c r="F102" s="19"/>
+      <c r="G102" s="19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7">
+      <c r="A103" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="B103" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C103" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D103" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E103" s="19">
+        <v>2</v>
+      </c>
+      <c r="F103" s="19">
+        <v>102325.79</v>
+      </c>
+      <c r="G103" s="19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7">
+      <c r="A104" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="B104" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="C104" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D104" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E104" s="19">
+        <v>10</v>
+      </c>
+      <c r="F104" s="19">
+        <v>46682.23</v>
+      </c>
+      <c r="G104" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7">
+      <c r="A105" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="B105" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C105" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D105" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E105" s="19">
+        <v>3</v>
+      </c>
+      <c r="F105" s="19">
+        <v>43273.57</v>
+      </c>
+      <c r="G105" s="19" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7">
+      <c r="A106" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="B106" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C106" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D106" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E106" s="19">
+        <v>5</v>
+      </c>
+      <c r="F106" s="19">
+        <v>8544.4</v>
+      </c>
+      <c r="G106" s="19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7">
+      <c r="A107" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="B107" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C107" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D107" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E107" s="19">
+        <v>1</v>
+      </c>
+      <c r="F107" s="19"/>
+      <c r="G107" s="19" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7">
+      <c r="A108" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="B108" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C108" s="19"/>
+      <c r="D108" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E108" s="19">
+        <v>7</v>
+      </c>
+      <c r="F108" s="19">
+        <v>11798.53</v>
+      </c>
+      <c r="G108" s="19" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7">
+      <c r="A109" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="B109" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C109" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D109" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E109" s="19">
+        <v>10</v>
+      </c>
+      <c r="F109" s="19"/>
+      <c r="G109" s="19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7">
+      <c r="A110" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="B110" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="C110" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D110" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E110" s="19">
+        <v>7</v>
+      </c>
+      <c r="F110" s="19"/>
+      <c r="G110" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7">
+      <c r="A111" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="B111" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C111" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D111" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E111" s="19">
+        <v>-2</v>
+      </c>
+      <c r="F111" s="19">
+        <v>11530.56</v>
+      </c>
+      <c r="G111" s="19"/>
+    </row>
+    <row r="112" spans="1:7">
+      <c r="A112" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="B112" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="C112" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D112" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E112" s="19">
+        <v>4</v>
+      </c>
+      <c r="F112" s="19">
+        <v>12451.69</v>
+      </c>
+      <c r="G112" s="19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7">
+      <c r="A113" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="B113" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C113" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D113" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E113" s="19">
+        <v>-2</v>
+      </c>
+      <c r="F113" s="19">
+        <v>14932.05</v>
+      </c>
+      <c r="G113" s="19" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7">
+      <c r="A114" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="B114" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="C114" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="D114" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E114" s="19">
+        <v>7</v>
+      </c>
+      <c r="F114" s="19">
+        <v>206884.76</v>
+      </c>
+      <c r="G114" s="19"/>
+    </row>
+    <row r="115" spans="1:7">
+      <c r="A115" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="B115" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C115" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D115" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E115" s="19">
+        <v>2</v>
+      </c>
+      <c r="F115" s="19"/>
+      <c r="G115" s="19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7">
+      <c r="A116" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="B116" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C116" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D116" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E116" s="19">
+        <v>6</v>
+      </c>
+      <c r="F116" s="19">
+        <v>71697.23</v>
+      </c>
+      <c r="G116" s="19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7">
+      <c r="A117" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="B117" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C117" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D117" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E117" s="19">
+        <v>3</v>
+      </c>
+      <c r="F117" s="19">
+        <v>7783.4</v>
+      </c>
+      <c r="G117" s="19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7">
+      <c r="A118" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="B118" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C118" s="19"/>
+      <c r="D118" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E118" s="19">
+        <v>-2</v>
+      </c>
+      <c r="F118" s="19">
+        <v>40092.550000000003</v>
+      </c>
+      <c r="G118" s="19"/>
+    </row>
+    <row r="119" spans="1:7">
+      <c r="A119" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="B119" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C119" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D119" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E119" s="19">
+        <v>10</v>
+      </c>
+      <c r="F119" s="19">
+        <v>49490.85</v>
+      </c>
+      <c r="G119" s="19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7">
+      <c r="A120" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="B120" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C120" s="19"/>
+      <c r="D120" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E120" s="19">
+        <v>5</v>
+      </c>
+      <c r="F120" s="19"/>
+      <c r="G120" s="19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7">
+      <c r="A121" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="B121" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="C121" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D121" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E121" s="19">
+        <v>6</v>
+      </c>
+      <c r="F121" s="19">
+        <v>105821.36</v>
+      </c>
+      <c r="G121" s="19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7">
+      <c r="A122" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="B122" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C122" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D122" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E122" s="19">
+        <v>1</v>
+      </c>
+      <c r="F122" s="19">
+        <v>108357.95</v>
+      </c>
+      <c r="G122" s="19"/>
+    </row>
+    <row r="123" spans="1:7">
+      <c r="A123" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="B123" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C123" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D123" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E123" s="19">
+        <v>8</v>
+      </c>
+      <c r="F123" s="19"/>
+      <c r="G123" s="19" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7">
+      <c r="A124" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="B124" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C124" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="D124" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E124" s="19">
+        <v>5</v>
+      </c>
+      <c r="F124" s="19"/>
+      <c r="G124" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7">
+      <c r="A125" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="B125" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C125" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="D125" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E125" s="19">
+        <v>2</v>
+      </c>
+      <c r="F125" s="19">
+        <v>181314.89</v>
+      </c>
+      <c r="G125" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7">
+      <c r="A126" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="B126" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C126" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D126" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E126" s="19">
+        <v>9</v>
+      </c>
+      <c r="F126" s="19">
+        <v>8132.34</v>
+      </c>
+      <c r="G126" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7">
+      <c r="A127" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="B127" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C127" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D127" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E127" s="19">
+        <v>5</v>
+      </c>
+      <c r="F127" s="19">
+        <v>11907.84</v>
+      </c>
+      <c r="G127" s="19"/>
+    </row>
+    <row r="128" spans="1:7">
+      <c r="A128" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="B128" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="C128" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D128" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E128" s="19">
+        <v>5</v>
+      </c>
+      <c r="F128" s="19"/>
+      <c r="G128" s="19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7">
+      <c r="A129" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="B129" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="C129" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D129" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E129" s="19">
+        <v>2</v>
+      </c>
+      <c r="F129" s="19"/>
+      <c r="G129" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7">
+      <c r="A130" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="B130" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C130" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="D130" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E130" s="19">
+        <v>10</v>
+      </c>
+      <c r="F130" s="19"/>
+      <c r="G130" s="19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7">
+      <c r="A131" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="B131" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C131" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D131" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E131" s="19">
+        <v>7</v>
+      </c>
+      <c r="F131" s="19">
+        <v>43599.72</v>
+      </c>
+      <c r="G131" s="19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7">
+      <c r="A132" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="B132" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C132" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D132" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E132" s="19">
+        <v>2</v>
+      </c>
+      <c r="F132" s="19"/>
+      <c r="G132" s="19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7">
+      <c r="A133" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="B133" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C133" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D133" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E133" s="19">
+        <v>2</v>
+      </c>
+      <c r="F133" s="19"/>
+      <c r="G133" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7">
+      <c r="A134" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="B134" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C134" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="D134" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E134" s="19">
+        <v>6</v>
+      </c>
+      <c r="F134" s="19">
+        <v>174757.36</v>
+      </c>
+      <c r="G134" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7">
+      <c r="A135" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="B135" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C135" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D135" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E135" s="19">
+        <v>8</v>
+      </c>
+      <c r="F135" s="19"/>
+      <c r="G135" s="19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7">
+      <c r="A136" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="B136" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="C136" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D136" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E136" s="19">
+        <v>7</v>
+      </c>
+      <c r="F136" s="19">
+        <v>95535.15</v>
+      </c>
+      <c r="G136" s="19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7">
+      <c r="A137" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="B137" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C137" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D137" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E137" s="19">
+        <v>6</v>
+      </c>
+      <c r="F137" s="19"/>
+      <c r="G137" s="19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7">
+      <c r="A138" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="B138" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C138" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D138" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E138" s="19">
+        <v>7</v>
+      </c>
+      <c r="F138" s="19">
+        <v>100398.88</v>
+      </c>
+      <c r="G138" s="19"/>
+    </row>
+    <row r="139" spans="1:7">
+      <c r="A139" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="B139" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="C139" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D139" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E139" s="19">
+        <v>4</v>
+      </c>
+      <c r="F139" s="19">
+        <v>100868.26</v>
+      </c>
+      <c r="G139" s="19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7">
+      <c r="A140" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="B140" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C140" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D140" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E140" s="19">
+        <v>3</v>
+      </c>
+      <c r="F140" s="19"/>
+      <c r="G140" s="19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7">
+      <c r="A141" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="B141" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C141" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D141" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E141" s="19">
+        <v>1</v>
+      </c>
+      <c r="F141" s="19">
+        <v>7032.07</v>
+      </c>
+      <c r="G141" s="19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7">
+      <c r="A142" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="B142" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C142" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D142" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E142" s="19">
+        <v>2</v>
+      </c>
+      <c r="F142" s="19">
+        <v>41152.379999999997</v>
+      </c>
+      <c r="G142" s="19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7">
+      <c r="A143" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="B143" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C143" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D143" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E143" s="19">
+        <v>5</v>
+      </c>
+      <c r="F143" s="19">
+        <v>9141.57</v>
+      </c>
+      <c r="G143" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7">
+      <c r="A144" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="B144" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C144" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D144" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E144" s="19">
+        <v>4</v>
+      </c>
+      <c r="F144" s="19">
+        <v>38949.17</v>
+      </c>
+      <c r="G144" s="19" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7">
+      <c r="A145" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="B145" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="C145" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D145" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E145" s="19">
+        <v>3</v>
+      </c>
+      <c r="F145" s="19"/>
+      <c r="G145" s="19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7">
+      <c r="A146" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="B146" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="C146" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D146" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E146" s="19">
+        <v>10</v>
+      </c>
+      <c r="F146" s="19">
+        <v>90314.29</v>
+      </c>
+      <c r="G146" s="19"/>
+    </row>
+    <row r="147" spans="1:7">
+      <c r="A147" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="B147" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C147" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D147" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E147" s="19">
+        <v>3</v>
+      </c>
+      <c r="F147" s="19">
+        <v>74388.37</v>
+      </c>
+      <c r="G147" s="19" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7">
+      <c r="A148" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="B148" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C148" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D148" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E148" s="19">
+        <v>3</v>
+      </c>
+      <c r="F148" s="19">
+        <v>8730.06</v>
+      </c>
+      <c r="G148" s="19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7">
+      <c r="A149" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="B149" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C149" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="D149" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E149" s="19">
+        <v>7</v>
+      </c>
+      <c r="F149" s="19">
+        <v>160385.10999999999</v>
+      </c>
+      <c r="G149" s="19" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7">
+      <c r="A150" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="B150" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C150" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D150" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E150" s="19">
+        <v>4</v>
+      </c>
+      <c r="F150" s="19">
+        <v>13391.8</v>
+      </c>
+      <c r="G150" s="19"/>
+    </row>
+    <row r="151" spans="1:7">
+      <c r="A151" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="B151" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C151" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D151" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E151" s="19">
+        <v>4</v>
+      </c>
+      <c r="F151" s="19">
+        <v>11515.53</v>
+      </c>
+      <c r="G151" s="19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7">
+      <c r="A152" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="B152" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C152" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D152" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E152" s="19">
+        <v>8</v>
+      </c>
+      <c r="F152" s="19">
+        <v>15570.79</v>
+      </c>
+      <c r="G152" s="19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7">
+      <c r="A153" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="B153" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C153" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="D153" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E153" s="19">
+        <v>7</v>
+      </c>
+      <c r="F153" s="19">
+        <v>157056.35</v>
+      </c>
+      <c r="G153" s="19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7">
+      <c r="A154" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="B154" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C154" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D154" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E154" s="19">
+        <v>2</v>
+      </c>
+      <c r="F154" s="19"/>
+      <c r="G154" s="19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7">
+      <c r="A155" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="B155" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="C155" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D155" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E155" s="19">
+        <v>10</v>
+      </c>
+      <c r="F155" s="19">
+        <v>10339.57</v>
+      </c>
+      <c r="G155" s="19"/>
+    </row>
+    <row r="156" spans="1:7">
+      <c r="A156" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="B156" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C156" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D156" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E156" s="19">
+        <v>3</v>
+      </c>
+      <c r="F156" s="19">
+        <v>8277.18</v>
+      </c>
+      <c r="G156" s="19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7">
+      <c r="A157" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="B157" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C157" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D157" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E157" s="19">
+        <v>9</v>
+      </c>
+      <c r="F157" s="19">
+        <v>389512.03</v>
+      </c>
+      <c r="G157" s="19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7">
+      <c r="A158" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="B158" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C158" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D158" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E158" s="19">
+        <v>4</v>
+      </c>
+      <c r="F158" s="19">
+        <v>400060.02</v>
+      </c>
+      <c r="G158" s="19"/>
+    </row>
+    <row r="159" spans="1:7">
+      <c r="A159" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="B159" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C159" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D159" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E159" s="19">
+        <v>5</v>
+      </c>
+      <c r="F159" s="19">
+        <v>50555.8</v>
+      </c>
+      <c r="G159" s="19"/>
+    </row>
+    <row r="160" spans="1:7">
+      <c r="A160" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="B160" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="C160" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D160" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E160" s="19">
+        <v>1</v>
+      </c>
+      <c r="F160" s="19"/>
+      <c r="G160" s="19" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7">
+      <c r="A161" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="B161" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="C161" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D161" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E161" s="19">
+        <v>8</v>
+      </c>
+      <c r="F161" s="19">
+        <v>16457.84</v>
+      </c>
+      <c r="G161" s="19"/>
+    </row>
+    <row r="162" spans="1:7">
+      <c r="A162" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="B162" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C162" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="D162" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E162" s="19">
+        <v>7</v>
+      </c>
+      <c r="F162" s="19">
+        <v>191512.58</v>
+      </c>
+      <c r="G162" s="19" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7">
+      <c r="A163" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="B163" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C163" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="D163" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E163" s="19">
+        <v>8</v>
+      </c>
+      <c r="F163" s="19">
+        <v>11122.12</v>
+      </c>
+      <c r="G163" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7">
+      <c r="A164" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B164" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C164" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D164" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E164" s="19">
+        <v>1</v>
+      </c>
+      <c r="F164" s="19">
+        <v>11947.97</v>
+      </c>
+      <c r="G164" s="19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7">
+      <c r="A165" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B165" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C165" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D165" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E165" s="19">
+        <v>2</v>
+      </c>
+      <c r="F165" s="19">
+        <v>39039.25</v>
+      </c>
+      <c r="G165" s="19"/>
+    </row>
+    <row r="166" spans="1:7">
+      <c r="A166" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B166" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C166" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D166" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E166" s="19">
+        <v>2</v>
+      </c>
+      <c r="F166" s="19">
+        <v>15076.76</v>
+      </c>
+      <c r="G166" s="19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7">
+      <c r="A167" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B167" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="C167" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D167" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E167" s="19">
+        <v>8</v>
+      </c>
+      <c r="F167" s="19">
+        <v>10406.06</v>
+      </c>
+      <c r="G167" s="19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7">
+      <c r="A168" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B168" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C168" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D168" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E168" s="19">
+        <v>9</v>
+      </c>
+      <c r="F168" s="19">
+        <v>14251.31</v>
+      </c>
+      <c r="G168" s="19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7">
+      <c r="A169" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B169" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C169" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D169" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E169" s="19">
+        <v>5</v>
+      </c>
+      <c r="F169" s="19">
+        <v>7279.27</v>
+      </c>
+      <c r="G169" s="19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7">
+      <c r="A170" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B170" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C170" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D170" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E170" s="19">
+        <v>1</v>
+      </c>
+      <c r="F170" s="19">
+        <v>357955</v>
+      </c>
+      <c r="G170" s="19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7">
+      <c r="A171" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B171" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="C171" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D171" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E171" s="19">
+        <v>8</v>
+      </c>
+      <c r="F171" s="19">
+        <v>14002.03</v>
+      </c>
+      <c r="G171" s="19" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7">
+      <c r="A172" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B172" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C172" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="D172" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E172" s="19">
+        <v>10</v>
+      </c>
+      <c r="F172" s="19">
+        <v>7374.96</v>
+      </c>
+      <c r="G172" s="19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7">
+      <c r="A173" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B173" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C173" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D173" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E173" s="19">
+        <v>5</v>
+      </c>
+      <c r="F173" s="19">
+        <v>93671.11</v>
+      </c>
+      <c r="G173" s="19"/>
+    </row>
+    <row r="174" spans="1:7">
+      <c r="A174" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B174" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C174" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D174" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E174" s="19">
+        <v>0</v>
+      </c>
+      <c r="F174" s="19">
+        <v>308409.15000000002</v>
+      </c>
+      <c r="G174" s="19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7">
+      <c r="A175" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B175" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C175" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="D175" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E175" s="19">
+        <v>4</v>
+      </c>
+      <c r="F175" s="19"/>
+      <c r="G175" s="19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7">
+      <c r="A176" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B176" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="C176" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D176" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E176" s="19">
+        <v>4</v>
+      </c>
+      <c r="F176" s="19"/>
+      <c r="G176" s="19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7">
+      <c r="A177" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B177" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C177" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D177" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E177" s="19">
+        <v>5</v>
+      </c>
+      <c r="F177" s="19">
+        <v>14746.09</v>
+      </c>
+      <c r="G177" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7">
+      <c r="A178" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B178" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C178" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D178" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E178" s="19">
+        <v>2</v>
+      </c>
+      <c r="F178" s="19"/>
+      <c r="G178" s="19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7">
+      <c r="A179" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B179" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C179" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D179" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E179" s="19">
+        <v>1</v>
+      </c>
+      <c r="F179" s="19">
+        <v>68379.14</v>
+      </c>
+      <c r="G179" s="19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7">
+      <c r="A180" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B180" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C180" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D180" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E180" s="19">
+        <v>9</v>
+      </c>
+      <c r="F180" s="19">
+        <v>48615.06</v>
+      </c>
+      <c r="G180" s="19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7">
+      <c r="A181" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B181" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C181" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D181" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E181" s="19">
+        <v>1</v>
+      </c>
+      <c r="F181" s="19">
+        <v>8182.45</v>
+      </c>
+      <c r="G181" s="19" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7">
+      <c r="A182" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B182" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C182" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D182" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E182" s="19">
+        <v>9</v>
+      </c>
+      <c r="F182" s="19"/>
+      <c r="G182" s="19" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7">
+      <c r="A183" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B183" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C183" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="D183" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E183" s="19">
+        <v>10</v>
+      </c>
+      <c r="F183" s="19">
+        <v>174464.25</v>
+      </c>
+      <c r="G183" s="19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7">
+      <c r="A184" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B184" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C184" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D184" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E184" s="19">
+        <v>7</v>
+      </c>
+      <c r="F184" s="19">
+        <v>368064.54</v>
+      </c>
+      <c r="G184" s="19" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7">
+      <c r="A185" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B185" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C185" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D185" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E185" s="19">
+        <v>4</v>
+      </c>
+      <c r="F185" s="19">
+        <v>42276.15</v>
+      </c>
+      <c r="G185" s="19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7">
+      <c r="A186" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B186" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C186" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D186" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E186" s="19">
+        <v>5</v>
+      </c>
+      <c r="F186" s="19">
+        <v>313046.23</v>
+      </c>
+      <c r="G186" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7">
+      <c r="A187" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B187" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C187" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D187" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E187" s="19">
+        <v>10</v>
+      </c>
+      <c r="F187" s="19">
+        <v>15333.05</v>
+      </c>
+      <c r="G187" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7">
+      <c r="A188" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B188" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C188" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D188" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E188" s="19">
+        <v>5</v>
+      </c>
+      <c r="F188" s="19">
+        <v>45084.14</v>
+      </c>
+      <c r="G188" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7">
+      <c r="A189" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B189" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="C189" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D189" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E189" s="19">
+        <v>10</v>
+      </c>
+      <c r="F189" s="19">
+        <v>16675.310000000001</v>
+      </c>
+      <c r="G189" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7">
+      <c r="A190" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B190" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C190" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D190" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E190" s="19">
+        <v>3</v>
+      </c>
+      <c r="F190" s="19"/>
+      <c r="G190" s="19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7">
+      <c r="A191" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B191" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C191" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D191" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E191" s="19">
+        <v>10</v>
+      </c>
+      <c r="F191" s="19">
+        <v>12990.1</v>
+      </c>
+      <c r="G191" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7">
+      <c r="A192" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B192" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C192" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D192" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E192" s="19">
+        <v>4</v>
+      </c>
+      <c r="F192" s="19">
+        <v>38345.57</v>
+      </c>
+      <c r="G192" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7">
+      <c r="A193" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B193" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="C193" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="D193" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E193" s="19">
+        <v>5</v>
+      </c>
+      <c r="F193" s="19">
+        <v>162828.26999999999</v>
+      </c>
+      <c r="G193" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7">
+      <c r="A194" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B194" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="C194" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D194" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E194" s="19">
+        <v>2</v>
+      </c>
+      <c r="F194" s="19">
+        <v>73330.59</v>
+      </c>
+      <c r="G194" s="19" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7">
+      <c r="A195" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B195" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C195" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D195" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E195" s="19">
+        <v>4</v>
+      </c>
+      <c r="F195" s="19">
+        <v>72885.58</v>
+      </c>
+      <c r="G195" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7">
+      <c r="A196" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B196" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C196" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D196" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E196" s="19">
+        <v>10</v>
+      </c>
+      <c r="F196" s="19">
+        <v>41015.83</v>
+      </c>
+      <c r="G196" s="19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7">
+      <c r="A197" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B197" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C197" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D197" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E197" s="19">
+        <v>3</v>
+      </c>
+      <c r="F197" s="19">
+        <v>89674.6</v>
+      </c>
+      <c r="G197" s="19"/>
+    </row>
+    <row r="198" spans="1:7">
+      <c r="A198" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B198" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C198" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D198" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E198" s="19">
+        <v>3</v>
+      </c>
+      <c r="F198" s="19">
+        <v>7618.03</v>
+      </c>
+      <c r="G198" s="19"/>
+    </row>
+    <row r="199" spans="1:7">
+      <c r="A199" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B199" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C199" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D199" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E199" s="19">
+        <v>2</v>
+      </c>
+      <c r="F199" s="19"/>
+      <c r="G199" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7">
+      <c r="A200" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B200" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C200" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D200" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E200" s="19">
+        <v>10</v>
+      </c>
+      <c r="F200" s="19"/>
+      <c r="G200" s="19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7">
+      <c r="A201" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B201" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="C201" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D201" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E201" s="19">
+        <v>-2</v>
+      </c>
+      <c r="F201" s="19">
+        <v>13164.24</v>
+      </c>
+      <c r="G201" s="19"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M200"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="9.453125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
@@ -6304,7 +10950,7 @@
     <col min="13" max="13" width="8.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -6339,7 +10985,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13">
       <c r="A2" s="1">
         <v>45663</v>
       </c>
@@ -6376,7 +11022,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13">
       <c r="A3" s="1">
         <v>45664</v>
       </c>
@@ -6413,7 +11059,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13">
       <c r="A4" s="1">
         <v>45664</v>
       </c>
@@ -6450,7 +11096,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13">
       <c r="A5" s="1">
         <v>45665</v>
       </c>
@@ -6487,7 +11133,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13">
       <c r="A6" s="1">
         <v>45665</v>
       </c>
@@ -6524,7 +11170,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13">
       <c r="A7" s="1">
         <v>45667</v>
       </c>
@@ -6561,7 +11207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13">
       <c r="A8" s="1">
         <v>45667</v>
       </c>
@@ -6592,7 +11238,7 @@
         <v>5507.1759999999995</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13">
       <c r="A9" s="1">
         <v>45668</v>
       </c>
@@ -6625,7 +11271,7 @@
       <c r="L9" s="10"/>
       <c r="M9" s="10"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13">
       <c r="A10" s="1">
         <v>45668</v>
       </c>
@@ -6657,7 +11303,7 @@
       </c>
       <c r="L10" s="6"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13">
       <c r="A11" s="1">
         <v>45669</v>
       </c>
@@ -6688,7 +11334,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13">
       <c r="A12" s="1">
         <v>45670</v>
       </c>
@@ -6721,7 +11367,7 @@
       <c r="J12" s="10"/>
       <c r="K12" s="10"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13">
       <c r="A13" s="1">
         <v>45672</v>
       </c>
@@ -6752,7 +11398,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13">
       <c r="A14" s="1">
         <v>45672</v>
       </c>
@@ -6783,7 +11429,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13">
       <c r="A15" s="1">
         <v>45673</v>
       </c>
@@ -6814,7 +11460,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13">
       <c r="A16" s="1">
         <v>45675</v>
       </c>
@@ -6845,7 +11491,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9">
       <c r="A17" s="1">
         <v>45675</v>
       </c>
@@ -6876,7 +11522,7 @@
         <v>18026.772000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9">
       <c r="A18" s="1">
         <v>45676</v>
       </c>
@@ -6907,7 +11553,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9">
       <c r="A19" s="1">
         <v>45680</v>
       </c>
@@ -6938,7 +11584,7 @@
         <v>77208.164000000004</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9">
       <c r="A20" s="1">
         <v>45680</v>
       </c>
@@ -6969,7 +11615,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9">
       <c r="A21" s="1">
         <v>45680</v>
       </c>
@@ -7000,7 +11646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9">
       <c r="A22" s="1">
         <v>45681</v>
       </c>
@@ -7031,7 +11677,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9">
       <c r="A23" s="1">
         <v>45681</v>
       </c>
@@ -7062,7 +11708,7 @@
         <v>15929.126000000002</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9">
       <c r="A24" s="1">
         <v>45682</v>
       </c>
@@ -7093,7 +11739,7 @@
         <v>9519.1535999999996</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9">
       <c r="A25" s="1">
         <v>45685</v>
       </c>
@@ -7124,7 +11770,7 @@
         <v>36563.217599999996</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9">
       <c r="A26" s="1">
         <v>45685</v>
       </c>
@@ -7155,7 +11801,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9">
       <c r="A27" s="1">
         <v>45685</v>
       </c>
@@ -7186,7 +11832,7 @@
         <v>116685.024</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9">
       <c r="A28" s="1">
         <v>45687</v>
       </c>
@@ -7217,7 +11863,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9">
       <c r="A29" s="1">
         <v>45687</v>
       </c>
@@ -7248,7 +11894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9">
       <c r="A30" s="1">
         <v>45688</v>
       </c>
@@ -7279,7 +11925,7 @@
         <v>153455.89199999999</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9">
       <c r="A31" s="1">
         <v>45689</v>
       </c>
@@ -7310,7 +11956,7 @@
         <v>8884.0479999999989</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9">
       <c r="A32" s="1">
         <v>45690</v>
       </c>
@@ -7341,7 +11987,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9">
       <c r="A33" s="1">
         <v>45690</v>
       </c>
@@ -7372,7 +12018,7 @@
         <v>38544.2592</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9">
       <c r="A34" s="1">
         <v>45691</v>
       </c>
@@ -7403,7 +12049,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9">
       <c r="A35" s="1">
         <v>45692</v>
       </c>
@@ -7434,7 +12080,7 @@
         <v>10704.302000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9">
       <c r="A36" s="1">
         <v>45692</v>
       </c>
@@ -7465,7 +12111,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9">
       <c r="A37" s="1">
         <v>45695</v>
       </c>
@@ -7496,7 +12142,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9">
       <c r="A38" s="1">
         <v>45695</v>
       </c>
@@ -7527,7 +12173,7 @@
         <v>17011.466</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9">
       <c r="A39" s="1">
         <v>45697</v>
       </c>
@@ -7558,7 +12204,7 @@
         <v>14659.998000000001</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9">
       <c r="A40" s="1">
         <v>45697</v>
       </c>
@@ -7589,7 +12235,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9">
       <c r="A41" s="1">
         <v>45697</v>
       </c>
@@ -7620,7 +12266,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9">
       <c r="A42" s="1">
         <v>45698</v>
       </c>
@@ -7651,7 +12297,7 @@
         <v>7635.6729999999998</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9">
       <c r="A43" s="1">
         <v>45698</v>
       </c>
@@ -7682,7 +12328,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9">
       <c r="A44" s="1">
         <v>45699</v>
       </c>
@@ -7713,7 +12359,7 @@
         <v>67762.316800000001</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9">
       <c r="A45" s="1">
         <v>45699</v>
       </c>
@@ -7744,7 +12390,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9">
       <c r="A46" s="1">
         <v>45701</v>
       </c>
@@ -7775,7 +12421,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9">
       <c r="A47" s="1">
         <v>45703</v>
       </c>
@@ -7806,7 +12452,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9">
       <c r="A48" s="1">
         <v>45704</v>
       </c>
@@ -7837,7 +12483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9">
       <c r="A49" s="1">
         <v>45706</v>
       </c>
@@ -7868,7 +12514,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:9">
       <c r="A50" s="1">
         <v>45706</v>
       </c>
@@ -7899,7 +12545,7 @@
         <v>63243.381999999991</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:9">
       <c r="A51" s="1">
         <v>45708</v>
       </c>
@@ -7930,7 +12576,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:9">
       <c r="A52" s="1">
         <v>45710</v>
       </c>
@@ -7961,7 +12607,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:9">
       <c r="A53" s="1">
         <v>45711</v>
       </c>
@@ -7992,7 +12638,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:9">
       <c r="A54" s="1">
         <v>45711</v>
       </c>
@@ -8023,7 +12669,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:9">
       <c r="A55" s="1">
         <v>45712</v>
       </c>
@@ -8054,7 +12700,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:9">
       <c r="A56" s="1">
         <v>45712</v>
       </c>
@@ -8085,7 +12731,7 @@
         <v>6392.0559999999996</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:9">
       <c r="A57" s="1">
         <v>45712</v>
       </c>
@@ -8116,7 +12762,7 @@
         <v>4487.2856000000002</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:9">
       <c r="A58" s="1">
         <v>45713</v>
       </c>
@@ -8147,7 +12793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:9">
       <c r="A59" s="1">
         <v>45714</v>
       </c>
@@ -8178,7 +12824,7 @@
         <v>10660.748</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:9">
       <c r="A60" s="1">
         <v>45715</v>
       </c>
@@ -8209,7 +12855,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:9">
       <c r="A61" s="1">
         <v>45716</v>
       </c>
@@ -8240,7 +12886,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:9">
       <c r="A62" s="1">
         <v>45717</v>
       </c>
@@ -8271,7 +12917,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:9">
       <c r="A63" s="1">
         <v>45719</v>
       </c>
@@ -8302,7 +12948,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:9">
       <c r="A64" s="1">
         <v>45720</v>
       </c>
@@ -8333,7 +12979,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:9">
       <c r="A65" s="1">
         <v>45720</v>
       </c>
@@ -8364,7 +13010,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:9">
       <c r="A66" s="1">
         <v>45720</v>
       </c>
@@ -8395,7 +13041,7 @@
         <v>142612.07940000002</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:9">
       <c r="A67" s="1">
         <v>45721</v>
       </c>
@@ -8426,7 +13072,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:9">
       <c r="A68" s="1">
         <v>45721</v>
       </c>
@@ -8457,7 +13103,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:9">
       <c r="A69" s="1">
         <v>45724</v>
       </c>
@@ -8488,7 +13134,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:9">
       <c r="A70" s="1">
         <v>45725</v>
       </c>
@@ -8519,7 +13165,7 @@
         <v>8438.4909000000007</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:9">
       <c r="A71" s="1">
         <v>45725</v>
       </c>
@@ -8550,7 +13196,7 @@
         <v>117330.63650000001</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:9">
       <c r="A72" s="1">
         <v>45727</v>
       </c>
@@ -8581,7 +13227,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:9">
       <c r="A73" s="1">
         <v>45728</v>
       </c>
@@ -8612,7 +13258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:9">
       <c r="A74" s="1">
         <v>45728</v>
       </c>
@@ -8643,7 +13289,7 @@
         <v>25795.812000000002</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:9">
       <c r="A75" s="1">
         <v>45729</v>
       </c>
@@ -8674,7 +13320,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:9">
       <c r="A76" s="1">
         <v>45730</v>
       </c>
@@ -8705,7 +13351,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:9">
       <c r="A77" s="1">
         <v>45731</v>
       </c>
@@ -8736,7 +13382,7 @@
         <v>109314.1044</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:9">
       <c r="A78" s="1">
         <v>45731</v>
       </c>
@@ -8767,7 +13413,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:9">
       <c r="A79" s="1">
         <v>45732</v>
       </c>
@@ -8798,7 +13444,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:9">
       <c r="A80" s="1">
         <v>45734</v>
       </c>
@@ -8829,7 +13475,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:9">
       <c r="A81" s="1">
         <v>45734</v>
       </c>
@@ -8860,7 +13506,7 @@
         <v>6261.0785999999998</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:9">
       <c r="A82" s="1">
         <v>45736</v>
       </c>
@@ -8891,7 +13537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:9">
       <c r="A83" s="1">
         <v>45736</v>
       </c>
@@ -8922,7 +13568,7 @@
         <v>34107.86</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:9">
       <c r="A84" s="1">
         <v>45739</v>
       </c>
@@ -8953,7 +13599,7 @@
         <v>96253.745999999999</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:9">
       <c r="A85" s="1">
         <v>45739</v>
       </c>
@@ -8984,7 +13630,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:9">
       <c r="A86" s="1">
         <v>45739</v>
       </c>
@@ -9015,7 +13661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:9">
       <c r="A87" s="1">
         <v>45740</v>
       </c>
@@ -9046,7 +13692,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:9">
       <c r="A88" s="1">
         <v>45740</v>
       </c>
@@ -9077,7 +13723,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:9">
       <c r="A89" s="1">
         <v>45741</v>
       </c>
@@ -9108,7 +13754,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:9">
       <c r="A90" s="1">
         <v>45743</v>
       </c>
@@ -9139,7 +13785,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:9">
       <c r="A91" s="1">
         <v>45745</v>
       </c>
@@ -9170,7 +13816,7 @@
         <v>72178.944600000003</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:9">
       <c r="A92" s="1">
         <v>45746</v>
       </c>
@@ -9201,7 +13847,7 @@
         <v>13777.422400000001</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:9">
       <c r="A93" s="1">
         <v>45748</v>
       </c>
@@ -9232,7 +13878,7 @@
         <v>20471.690000000002</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:9">
       <c r="A94" s="1">
         <v>45748</v>
       </c>
@@ -9263,7 +13909,7 @@
         <v>16075.553400000001</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:9">
       <c r="A95" s="1">
         <v>45750</v>
       </c>
@@ -9294,7 +13940,7 @@
         <v>15402.35</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:9">
       <c r="A96" s="1">
         <v>45750</v>
       </c>
@@ -9325,7 +13971,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:9">
       <c r="A97" s="1">
         <v>45750</v>
       </c>
@@ -9356,7 +14002,7 @@
         <v>29472.188399999999</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:9">
       <c r="A98" s="1">
         <v>45750</v>
       </c>
@@ -9387,7 +14033,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:9">
       <c r="A99" s="1">
         <v>45750</v>
       </c>
@@ -9418,7 +14064,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:9">
       <c r="A100" s="1">
         <v>45751</v>
       </c>
@@ -9449,7 +14095,7 @@
         <v>10645.009199999999</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:9">
       <c r="A101" s="1">
         <v>45751</v>
       </c>
@@ -9480,7 +14126,7 @@
         <v>42063.471999999994</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:9">
       <c r="A102" s="1">
         <v>45753</v>
       </c>
@@ -9511,7 +14157,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:9">
       <c r="A103" s="1">
         <v>45753</v>
       </c>
@@ -9542,7 +14188,7 @@
         <v>14325.6106</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:9">
       <c r="A104" s="1">
         <v>45754</v>
       </c>
@@ -9573,7 +14219,7 @@
         <v>32677.561000000005</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:9">
       <c r="A105" s="1">
         <v>45754</v>
       </c>
@@ -9604,7 +14250,7 @@
         <v>5192.8283999999994</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:9">
       <c r="A106" s="1">
         <v>45754</v>
       </c>
@@ -9635,7 +14281,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:9">
       <c r="A107" s="1">
         <v>45754</v>
       </c>
@@ -9666,7 +14312,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:9">
       <c r="A108" s="1">
         <v>45756</v>
       </c>
@@ -9697,7 +14343,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:9">
       <c r="A109" s="1">
         <v>45756</v>
       </c>
@@ -9728,7 +14374,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:9">
       <c r="A110" s="1">
         <v>45756</v>
       </c>
@@ -9759,7 +14405,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:9">
       <c r="A111" s="1">
         <v>45756</v>
       </c>
@@ -9790,7 +14436,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:9">
       <c r="A112" s="1">
         <v>45757</v>
       </c>
@@ -9821,7 +14467,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:9">
       <c r="A113" s="1">
         <v>45757</v>
       </c>
@@ -9852,7 +14498,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:9">
       <c r="A114" s="1">
         <v>45758</v>
       </c>
@@ -9883,7 +14529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:9">
       <c r="A115" s="1">
         <v>45758</v>
       </c>
@@ -9914,7 +14560,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:9">
       <c r="A116" s="1">
         <v>45759</v>
       </c>
@@ -9945,7 +14591,7 @@
         <v>34414.670400000003</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:9">
       <c r="A117" s="1">
         <v>45761</v>
       </c>
@@ -9976,7 +14622,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:9">
       <c r="A118" s="1">
         <v>45761</v>
       </c>
@@ -10007,7 +14653,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:9">
       <c r="A119" s="1">
         <v>45762</v>
       </c>
@@ -10038,7 +14684,7 @@
         <v>19796.34</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:9">
       <c r="A120" s="1">
         <v>45763</v>
       </c>
@@ -10069,7 +14715,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:9">
       <c r="A121" s="1">
         <v>45763</v>
       </c>
@@ -10100,7 +14746,7 @@
         <v>50794.252800000002</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:9">
       <c r="A122" s="1">
         <v>45764</v>
       </c>
@@ -10131,7 +14777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:9">
       <c r="A123" s="1">
         <v>45765</v>
       </c>
@@ -10162,7 +14808,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:9">
       <c r="A124" s="1">
         <v>45768</v>
       </c>
@@ -10193,7 +14839,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:9">
       <c r="A125" s="1">
         <v>45769</v>
       </c>
@@ -10224,7 +14870,7 @@
         <v>21757.786800000002</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:9">
       <c r="A126" s="1">
         <v>45769</v>
       </c>
@@ -10255,7 +14901,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:9">
       <c r="A127" s="1">
         <v>45770</v>
       </c>
@@ -10286,7 +14932,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:9">
       <c r="A128" s="1">
         <v>45771</v>
       </c>
@@ -10317,7 +14963,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:9">
       <c r="A129" s="1">
         <v>45772</v>
       </c>
@@ -10348,7 +14994,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:9">
       <c r="A130" s="1">
         <v>45772</v>
       </c>
@@ -10379,7 +15025,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:9">
       <c r="A131" s="1">
         <v>45773</v>
       </c>
@@ -10410,7 +15056,7 @@
         <v>15259.902000000002</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:9">
       <c r="A132" s="1">
         <v>45773</v>
       </c>
@@ -10441,7 +15087,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:9">
       <c r="A133" s="1">
         <v>45774</v>
       </c>
@@ -10472,7 +15118,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:9">
       <c r="A134" s="1">
         <v>45774</v>
       </c>
@@ -10503,7 +15149,7 @@
         <v>73398.091199999995</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:9">
       <c r="A135" s="1">
         <v>45775</v>
       </c>
@@ -10534,7 +15180,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:9">
       <c r="A136" s="1">
         <v>45776</v>
       </c>
@@ -10565,7 +15211,7 @@
         <v>33437.302499999998</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:9">
       <c r="A137" s="1">
         <v>45776</v>
       </c>
@@ -10596,7 +15242,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:9">
       <c r="A138" s="1">
         <v>45778</v>
       </c>
@@ -10627,7 +15273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:9">
       <c r="A139" s="1">
         <v>45780</v>
       </c>
@@ -10658,7 +15304,7 @@
         <v>20173.652000000002</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:9">
       <c r="A140" s="1">
         <v>45781</v>
       </c>
@@ -10689,7 +15335,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:9">
       <c r="A141" s="1">
         <v>45783</v>
       </c>
@@ -10720,7 +15366,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:9">
       <c r="A142" s="1">
         <v>45784</v>
       </c>
@@ -10751,7 +15397,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:9">
       <c r="A143" s="1">
         <v>45785</v>
       </c>
@@ -10782,7 +15428,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:9">
       <c r="A144" s="1">
         <v>45786</v>
       </c>
@@ -10813,7 +15459,7 @@
         <v>6231.8671999999997</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:9">
       <c r="A145" s="1">
         <v>45786</v>
       </c>
@@ -10844,7 +15490,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:9">
       <c r="A146" s="1">
         <v>45787</v>
       </c>
@@ -10875,7 +15521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:9">
       <c r="A147" s="1">
         <v>45788</v>
       </c>
@@ -10906,7 +15552,7 @@
         <v>8926.6044000000002</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:9">
       <c r="A148" s="1">
         <v>45788</v>
       </c>
@@ -10937,7 +15583,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:9">
       <c r="A149" s="1">
         <v>45789</v>
       </c>
@@ -10968,7 +15614,7 @@
         <v>44907.830800000003</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:9">
       <c r="A150" s="1">
         <v>45793</v>
       </c>
@@ -10999,7 +15645,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:9">
       <c r="A151" s="1">
         <v>45793</v>
       </c>
@@ -11030,7 +15676,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:9">
       <c r="A152" s="1">
         <v>45794</v>
       </c>
@@ -11061,7 +15707,7 @@
         <v>4982.6528000000008</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:9">
       <c r="A153" s="1">
         <v>45794</v>
       </c>
@@ -11092,7 +15738,7 @@
         <v>54969.722500000003</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:9">
       <c r="A154" s="1">
         <v>45795</v>
       </c>
@@ -11123,7 +15769,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:9">
       <c r="A155" s="1">
         <v>45796</v>
       </c>
@@ -11154,7 +15800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:9">
       <c r="A156" s="1">
         <v>45796</v>
       </c>
@@ -11185,7 +15831,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:9">
       <c r="A157" s="1">
         <v>45801</v>
       </c>
@@ -11216,7 +15862,7 @@
         <v>280448.66160000005</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:9">
       <c r="A158" s="1">
         <v>45801</v>
       </c>
@@ -11247,7 +15893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:9">
       <c r="A159" s="1">
         <v>45802</v>
       </c>
@@ -11278,7 +15924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:9">
       <c r="A160" s="1">
         <v>45802</v>
       </c>
@@ -11309,7 +15955,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:9">
       <c r="A161" s="1">
         <v>45805</v>
       </c>
@@ -11340,7 +15986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:9">
       <c r="A162" s="1">
         <v>45806</v>
       </c>
@@ -11371,7 +16017,7 @@
         <v>53623.522399999994</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:9">
       <c r="A163" s="1">
         <v>45807</v>
       </c>
@@ -11402,7 +16048,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:9">
       <c r="A164" s="1" t="s">
         <v>19</v>
       </c>
@@ -11433,7 +16079,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:9">
       <c r="A165" s="1" t="s">
         <v>19</v>
       </c>
@@ -11464,7 +16110,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:9">
       <c r="A166" s="1" t="s">
         <v>19</v>
       </c>
@@ -11495,7 +16141,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:9">
       <c r="A167" s="1" t="s">
         <v>19</v>
       </c>
@@ -11526,7 +16172,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:9">
       <c r="A168" s="1" t="s">
         <v>19</v>
       </c>
@@ -11557,7 +16203,7 @@
         <v>8978.3253000000004</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:9">
       <c r="A169" s="1" t="s">
         <v>19</v>
       </c>
@@ -11588,7 +16234,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:9">
       <c r="A170" s="1" t="s">
         <v>19</v>
       </c>
@@ -11619,7 +16265,7 @@
         <v>14318.2</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:9">
       <c r="A171" s="1" t="s">
         <v>19</v>
       </c>
@@ -11650,7 +16296,7 @@
         <v>4480.6496000000006</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:9">
       <c r="A172" s="1" t="s">
         <v>19</v>
       </c>
@@ -11681,7 +16327,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:9">
       <c r="A173" s="1" t="s">
         <v>19</v>
       </c>
@@ -11712,7 +16358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:9">
       <c r="A174" s="1" t="s">
         <v>19</v>
       </c>
@@ -11743,7 +16389,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:9">
       <c r="A175" s="1" t="s">
         <v>19</v>
       </c>
@@ -11774,7 +16420,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:9">
       <c r="A176" s="1" t="s">
         <v>19</v>
       </c>
@@ -11805,7 +16451,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:9">
       <c r="A177" s="1" t="s">
         <v>19</v>
       </c>
@@ -11836,7 +16482,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:9">
       <c r="A178" s="1" t="s">
         <v>19</v>
       </c>
@@ -11867,7 +16513,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:9">
       <c r="A179" s="1" t="s">
         <v>19</v>
       </c>
@@ -11898,7 +16544,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:9">
       <c r="A180" s="1" t="s">
         <v>19</v>
       </c>
@@ -11929,7 +16575,7 @@
         <v>30627.487800000003</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:9">
       <c r="A181" s="1" t="s">
         <v>19</v>
       </c>
@@ -11960,7 +16606,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:9">
       <c r="A182" s="1" t="s">
         <v>19</v>
       </c>
@@ -11991,7 +16637,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:9">
       <c r="A183" s="1" t="s">
         <v>19</v>
       </c>
@@ -12022,7 +16668,7 @@
         <v>69785.7</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:9">
       <c r="A184" s="1" t="s">
         <v>19</v>
       </c>
@@ -12053,7 +16699,7 @@
         <v>103058.07119999999</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:9">
       <c r="A185" s="1" t="s">
         <v>19</v>
       </c>
@@ -12084,7 +16730,7 @@
         <v>13528.368</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:9">
       <c r="A186" s="1" t="s">
         <v>19</v>
       </c>
@@ -12115,7 +16761,7 @@
         <v>109566.1805</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:9">
       <c r="A187" s="1" t="s">
         <v>19</v>
       </c>
@@ -12146,7 +16792,7 @@
         <v>10733.135</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:9">
       <c r="A188" s="1" t="s">
         <v>19</v>
       </c>
@@ -12177,7 +16823,7 @@
         <v>15779.449000000002</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:9">
       <c r="A189" s="1" t="s">
         <v>19</v>
       </c>
@@ -12208,7 +16854,7 @@
         <v>11672.717000000002</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:9">
       <c r="A190" s="1" t="s">
         <v>19</v>
       </c>
@@ -12239,7 +16885,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:9">
       <c r="A191" s="1" t="s">
         <v>19</v>
       </c>
@@ -12270,7 +16916,7 @@
         <v>9093.0700000000015</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:9">
       <c r="A192" s="1" t="s">
         <v>19</v>
       </c>
@@ -12301,7 +16947,7 @@
         <v>10736.759600000001</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:9">
       <c r="A193" s="1" t="s">
         <v>19</v>
       </c>
@@ -12332,7 +16978,7 @@
         <v>56989.894500000002</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:9">
       <c r="A194" s="1" t="s">
         <v>19</v>
       </c>
@@ -12363,7 +17009,7 @@
         <v>5866.4471999999996</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:9">
       <c r="A195" s="1" t="s">
         <v>19</v>
       </c>
@@ -12394,7 +17040,7 @@
         <v>17492.539199999999</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:9">
       <c r="A196" s="1" t="s">
         <v>19</v>
       </c>
@@ -12425,7 +17071,7 @@
         <v>20507.915000000005</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:9">
       <c r="A197" s="1" t="s">
         <v>19</v>
       </c>
@@ -12456,7 +17102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:9">
       <c r="A198" s="1" t="s">
         <v>19</v>
       </c>
@@ -12487,7 +17133,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:9">
       <c r="A199" s="1" t="s">
         <v>19</v>
       </c>
@@ -12518,7 +17164,7 @@
         <v>No Discount</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:9">
       <c r="A200" s="1" t="s">
         <v>19</v>
       </c>
@@ -12561,10 +17207,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J17"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="16.08984375" customWidth="1"/>
     <col min="2" max="2" width="16.08984375" bestFit="1" customWidth="1"/>
@@ -12576,10 +17222,10 @@
     <col min="10" max="10" width="16.08984375" style="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10">
       <c r="A1" s="6"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10">
       <c r="A3" s="5" t="s">
         <v>33</v>
       </c>
@@ -12602,7 +17248,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10">
       <c r="A4" s="6">
         <v>64049736.120000012</v>
       </c>
@@ -12625,7 +17271,7 @@
         <v>22228499.18</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10">
       <c r="C5" s="3" t="s">
         <v>11</v>
       </c>
@@ -12645,7 +17291,7 @@
         <v>8316228.0499999989</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10">
       <c r="C6" s="3" t="s">
         <v>15</v>
       </c>
@@ -12665,7 +17311,7 @@
         <v>4004582.74</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10">
       <c r="F7" s="3" t="s">
         <v>19</v>
       </c>
@@ -12679,7 +17325,7 @@
         <v>9658059.0999999978</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10">
       <c r="F8" s="3" t="s">
         <v>22</v>
       </c>
@@ -12693,7 +17339,7 @@
         <v>11192963.720000004</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10">
       <c r="A9" s="4" t="s">
         <v>34</v>
       </c>
@@ -12713,7 +17359,7 @@
         <v>8649403.3300000001</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10">
       <c r="A10" s="3" t="s">
         <v>7</v>
       </c>
@@ -12727,7 +17373,7 @@
         <v>6984522.7499999991</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10">
       <c r="A11" s="3" t="s">
         <v>25</v>
       </c>
@@ -12741,7 +17387,7 @@
         <v>11244209.02</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10">
       <c r="A12" s="3" t="s">
         <v>29</v>
       </c>
@@ -12755,7 +17401,7 @@
         <v>28281652.920000002</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10">
       <c r="A13" s="3" t="s">
         <v>27</v>
       </c>
@@ -12763,7 +17409,7 @@
         <v>8554345.6199999992</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10">
       <c r="A14" s="3" t="s">
         <v>20</v>
       </c>
@@ -12771,7 +17417,7 @@
         <v>14001734.729999999</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10">
       <c r="A15" s="3" t="s">
         <v>28</v>
       </c>
@@ -12779,7 +17425,7 @@
         <v>6503761.9100000001</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10">
       <c r="A16" s="3" t="s">
         <v>31</v>
       </c>
@@ -12787,7 +17433,7 @@
         <v>6338067.6499999994</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2">
       <c r="A17" s="3" t="s">
         <v>30</v>
       </c>
@@ -12801,12 +17447,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="H1:O12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
-    <row r="1" spans="8:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="8:15">
       <c r="H1" s="16" t="s">
         <v>36</v>
       </c>
@@ -12818,7 +17464,7 @@
       <c r="N1" s="17"/>
       <c r="O1" s="17"/>
     </row>
-    <row r="2" spans="8:15" x14ac:dyDescent="0.35">
+    <row r="2" spans="8:15">
       <c r="H2" s="17"/>
       <c r="I2" s="17"/>
       <c r="J2" s="17"/>
@@ -12828,10 +17474,10 @@
       <c r="N2" s="17"/>
       <c r="O2" s="17"/>
     </row>
-    <row r="4" spans="8:15" x14ac:dyDescent="0.35">
+    <row r="4" spans="8:15">
       <c r="I4" s="13"/>
     </row>
-    <row r="12" spans="8:15" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="12" spans="8:15" ht="18.5">
       <c r="I12" s="7"/>
     </row>
   </sheetData>
